--- a/www/download/COUNTRY.FIN.rpA1.xlsx
+++ b/www/download/COUNTRY.FIN.rpA1.xlsx
@@ -342,7 +342,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AC37"/>
+  <dimension ref="A1:AC55"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -500,7 +500,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>Finlândia</t>
         </is>
       </c>
     </row>
@@ -510,6 +510,11 @@
           <t>Computation method</t>
         </is>
       </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Reduction Problem: Alternative 1</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -847,2523 +852,4084 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Capital depreciation (USD)</t>
+          <t>Exchange rate (USD)</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>capital_depreciation.s.us</t>
+          <t>exchange.r.us</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>0.029</t>
+          <t>0.733573431220508</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>0.026</t>
+          <t>0.772272322275964</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>0.024</t>
+          <t>0.871915557756043</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>0.024</t>
+          <t>0.89762575613992</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>0.022</t>
+          <t>0.938262378300011</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>0.02</t>
+          <t>1.08271976614765</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>0.022</t>
+          <t>1.11656987699161</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>0.022</t>
+          <t>1.05752963905731</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>0.027</t>
+          <t>0.884017007086561</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>0.03</t>
+          <t>0.803923182182888</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>0.03</t>
+          <t>0.803793922960251</t>
         </is>
       </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>0.031</t>
+          <t>0.796431999450991</t>
         </is>
       </c>
       <c r="O9" t="inlineStr">
         <is>
-          <t>0.036</t>
+          <t>0.729660723656212</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.67990207486318</t>
         </is>
       </c>
       <c r="Q9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.716948692920124</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Number of employee</t>
+          <t>Rate of surplus value of high-skilled employee</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>emp.s.un</t>
+          <t>surplus_value.empe_hs.r.pc</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>2.053</t>
+          <t>0.108150333559031</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>2.082</t>
+          <t>0.0859706766995654</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>2.153</t>
+          <t>0.307138086395737</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>2.193</t>
+          <t>0.210478519906325</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>2.247</t>
+          <t>0.177878423134171</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>2.293</t>
+          <t>0.292207178454259</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>2.324</t>
+          <t>0.270888530075221</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>2.346</t>
+          <t>0.253102802454486</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>2.348</t>
+          <t>0.170143330681261</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>2.357</t>
+          <t>0.0646219510838297</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>2.389</t>
+          <t>0.0365814194201133</t>
         </is>
       </c>
       <c r="N10" t="inlineStr">
         <is>
-          <t>2.433</t>
+          <t>-0.00150093003249585</t>
         </is>
       </c>
       <c r="O10" t="inlineStr">
         <is>
-          <t>2.486</t>
+          <t>-0.00833989487453224</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>2.541</t>
+          <t>0.0154083061026682</t>
         </is>
       </c>
       <c r="Q10" t="inlineStr">
         <is>
-          <t>2.468</t>
+          <t>0.0785290297999566</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Number of persons engaged</t>
+          <t>Rate of surplus value of medium-skilled employee</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>empe.s.un</t>
+          <t>surplus_value.empe_ms.r.pc</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>1.772</t>
+          <t>0.461884793825778</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>1.799</t>
+          <t>0.433299130277399</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>1.865</t>
+          <t>0.712450530756305</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>1.92</t>
+          <t>0.604087965663453</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>1.968</t>
+          <t>0.610577032280576</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>2.013</t>
+          <t>0.783143569519414</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>2.051</t>
+          <t>0.720306134461092</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>2.076</t>
+          <t>0.70600157697204</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>2.08</t>
+          <t>0.522871973976405</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>2.088</t>
+          <t>0.48438689425183</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>2.119</t>
+          <t>0.464647522128491</t>
         </is>
       </c>
       <c r="N11" t="inlineStr">
         <is>
-          <t>2.153</t>
+          <t>0.424790033418099</t>
         </is>
       </c>
       <c r="O11" t="inlineStr">
         <is>
-          <t>2.201</t>
+          <t>0.467416880160428</t>
         </is>
       </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>2.234</t>
+          <t>0.522869996645882</t>
         </is>
       </c>
       <c r="Q11" t="inlineStr">
         <is>
-          <t>2.157</t>
+          <t>0.625949029418833</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Total hours worked by persons engaged</t>
+          <t>Rate of surplus value of low-skilled employee</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>hours_worked.emp.s.hr</t>
+          <t>surplus_value.empe_ls.r.pc</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>3645.8</t>
+          <t>0.429778858029916</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>3695.2</t>
+          <t>0.409065351884138</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>3811.8</t>
+          <t>0.687372405005517</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>3860.6</t>
+          <t>0.639885364969683</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>3964.7</t>
+          <t>0.663872317796626</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>4014.9</t>
+          <t>0.862804993598142</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>4027.8</t>
+          <t>0.79821203836436</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>4049.8</t>
+          <t>0.790710239035032</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>4034.9</t>
+          <t>0.494975724674651</t>
         </is>
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>4061.5</t>
+          <t>0.556543399544837</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>4099.4</t>
+          <t>0.528398323749983</t>
         </is>
       </c>
       <c r="N12" t="inlineStr">
         <is>
-          <t>4157.8</t>
+          <t>0.47910377745003</t>
         </is>
       </c>
       <c r="O12" t="inlineStr">
         <is>
-          <t>4242.2</t>
+          <t>0.468573276092316</t>
         </is>
       </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>4292.752</t>
+          <t>0.477175760666443</t>
         </is>
       </c>
       <c r="Q12" t="inlineStr">
         <is>
-          <t>4119.799</t>
+          <t>0.571714374076839</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Total hours worked by employees</t>
+          <t>Gross output (magnitude of value)</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>hours_worked.empe.s.hr</t>
+          <t>gross_output.s.mv</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>2929</t>
+          <t>6717255368.38918</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>2963.1</t>
+          <t>6597238238.88994</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>3079.1</t>
+          <t>6429135638.83179</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>3160.6</t>
+          <t>6839987420.07982</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>3234.5</t>
+          <t>7240457144.52789</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>3295</t>
+          <t>7279794240.19296</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>3338.8</t>
+          <t>6964995797.95902</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>3372.6</t>
+          <t>6879372720.20278</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>3374.3</t>
+          <t>7229550754.76425</t>
         </is>
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>3397.5</t>
+          <t>7429943756.37025</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>3436.3</t>
+          <t>7667354336.14852</t>
         </is>
       </c>
       <c r="N13" t="inlineStr">
         <is>
-          <t>3485.8</t>
+          <t>8025579468.9062</t>
         </is>
       </c>
       <c r="O13" t="inlineStr">
         <is>
-          <t>3563.4</t>
+          <t>8171624262.67934</t>
         </is>
       </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>3620.7</t>
+          <t>7656678623.25369</t>
         </is>
       </c>
       <c r="Q13" t="inlineStr">
         <is>
-          <t>3434.5</t>
+          <t>5668043635.38076</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Share of high-skilled labour compensation</t>
+          <t>Total labour force value (magnitude of value)</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>compensation.empe_hs.r.pc</t>
+          <t>labour_force_value.s.mv</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>31.88</t>
+          <t>2225828861.63571</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>32.52</t>
+          <t>2297253985.87467</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>32.9</t>
+          <t>1992342884.12835</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>33.46</t>
+          <t>2173668779.53822</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>34.56</t>
+          <t>2240831509.4752</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>34.74</t>
+          <t>2065374492.33667</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>34.85</t>
+          <t>2156951635.90644</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>35.37</t>
+          <t>2205324058.02163</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>34.12</t>
+          <t>2460168082.02869</t>
         </is>
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>37.06</t>
+          <t>2592969978.84907</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>37.41</t>
+          <t>2676936573.19358</t>
         </is>
       </c>
       <c r="N14" t="inlineStr">
         <is>
-          <t>37.91</t>
+          <t>2810379017.35258</t>
         </is>
       </c>
       <c r="O14" t="inlineStr">
         <is>
-          <t>39.62</t>
+          <t>2860781192.74195</t>
         </is>
       </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>40.32</t>
+          <t>2833959161.18656</t>
         </is>
       </c>
       <c r="Q14" t="inlineStr">
         <is>
-          <t>42.02</t>
+          <t>2540982304.34147</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Share of medium-skilled labour compensation</t>
+          <t>Value per output</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>compensation.empe_ms.r.pc</t>
+          <t>value.m.mv</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>40.27</t>
+          <t>987894.540243692</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>40.87</t>
+          <t>984791.736986844</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>41.49</t>
+          <t>998592.001260864</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>41.89</t>
+          <t>1032262.54679044</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>41.98</t>
+          <t>1131833.22341389</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>42.63</t>
+          <t>1173597.08680779</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>43.21</t>
+          <t>1117487.877754</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>43.53</t>
+          <t>1045164.32011892</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>43.99</t>
+          <t>932100.048139635</t>
         </is>
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>44.27</t>
+          <t>815831.668302057</t>
         </is>
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>44.24</t>
+          <t>796217.213247507</t>
         </is>
       </c>
       <c r="N15" t="inlineStr">
         <is>
-          <t>44.42</t>
+          <t>753937.533054768</t>
         </is>
       </c>
       <c r="O15" t="inlineStr">
         <is>
-          <t>43.04</t>
+          <t>636141.016245439</t>
         </is>
       </c>
       <c r="P15" t="inlineStr">
         <is>
-          <t>42.7</t>
+          <t>532710.525846113</t>
         </is>
       </c>
       <c r="Q15" t="inlineStr">
         <is>
-          <t>42.3</t>
+          <t>491430.989517422</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Share of low-skilled labour compensation</t>
+          <t>Gross Domestic Product (direct prices - USD)</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>compensation.empe_ls.r.pc</t>
+          <t>gdp.s.du</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>27.85</t>
+          <t>17177.8669219308</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>26.6</t>
+          <t>17350.3273040876</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>25.62</t>
+          <t>17733.7550174455</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>24.65</t>
+          <t>17803.530210708</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>23.46</t>
+          <t>18928.1121222997</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>22.63</t>
+          <t>19394.2854661761</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>21.94</t>
+          <t>18782.4892652337</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>21.1</t>
+          <t>19147.5241429258</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>21.89</t>
+          <t>20366.1444272394</t>
         </is>
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>18.67</t>
+          <t>22476.5363029394</t>
         </is>
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>18.35</t>
+          <t>24173.9121467651</t>
         </is>
       </c>
       <c r="N16" t="inlineStr">
         <is>
-          <t>17.66</t>
+          <t>25709.6977804153</t>
         </is>
       </c>
       <c r="O16" t="inlineStr">
         <is>
-          <t>17.34</t>
+          <t>29528.7472154658</t>
         </is>
       </c>
       <c r="P16" t="inlineStr">
         <is>
-          <t>16.99</t>
+          <t>33063.9908043842</t>
         </is>
       </c>
       <c r="Q16" t="inlineStr">
         <is>
-          <t>15.68</t>
+          <t>29142.6243385052</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Share of hours worked by high-skilled persons engaged</t>
+          <t>Gross output (direct prices - USD)</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>hours_worked.empe_hs.r.pc</t>
+          <t>gross_output.s.du</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>27.4</t>
+          <t>52289.898399789</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>28.02</t>
+          <t>51739.9280150896</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>28.33</t>
+          <t>50097.8629022633</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>28.27</t>
+          <t>53010.5879654596</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>28.5</t>
+          <t>58440.2305438274</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>28.54</t>
+          <t>59974.6857097518</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>28.88</t>
+          <t>55872.5372886151</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>29.27</t>
+          <t>56414.8165866922</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>29.73</t>
+          <t>63866.6065826262</t>
         </is>
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>30.36</t>
+          <t>72337.9539846026</t>
         </is>
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>30.45</t>
+          <t>79947.3559869621</t>
         </is>
       </c>
       <c r="N17" t="inlineStr">
         <is>
-          <t>30.8</t>
+          <t>87708.915051343</t>
         </is>
       </c>
       <c r="O17" t="inlineStr">
         <is>
-          <t>31.69</t>
+          <t>101020.609223991</t>
         </is>
       </c>
       <c r="P17" t="inlineStr">
         <is>
-          <t>32.03</t>
+          <t>104799.560392045</t>
         </is>
       </c>
       <c r="Q17" t="inlineStr">
         <is>
-          <t>33.73</t>
+          <t>72368.4081409804</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Share of hours worked by medium-skilled persons engaged</t>
+          <t>Rate of surplus value</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>hours_worked.empe_ms.r.pc</t>
+          <t>surplus_value.empe.r.pc</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>43.53</t>
+          <t>0.315914287250077</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>44.16</t>
+          <t>0.289844317702558</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>44.81</t>
+          <t>0.545466909601312</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>45.06</t>
+          <t>0.454039377918215</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>45.61</t>
+          <t>0.4434373964857</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>46.31</t>
+          <t>0.595352325801307</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>46.7</t>
+          <t>0.547925296246569</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>47.12</t>
+          <t>0.529299055951674</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>47.68</t>
+          <t>0.371572952534813</t>
         </is>
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>48.57</t>
+          <t>0.310273558010121</t>
         </is>
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>48.79</t>
+          <t>0.283668815470102</t>
         </is>
       </c>
       <c r="N18" t="inlineStr">
         <is>
-          <t>49.15</t>
+          <t>0.240330922796197</t>
         </is>
       </c>
       <c r="O18" t="inlineStr">
         <is>
-          <t>48.94</t>
+          <t>0.245603826339693</t>
         </is>
       </c>
       <c r="P18" t="inlineStr">
         <is>
-          <t>49.09</t>
+          <t>0.277611918191521</t>
         </is>
       </c>
       <c r="Q18" t="inlineStr">
         <is>
-          <t>48.71</t>
+          <t>0.3516426281804</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Share of hours worked by low-skilled persons engaged</t>
+          <t>Capital depreciation (USD)</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>hours_worked.empe_ls.r.pc</t>
+          <t>capital_depreciation.s.us</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>29.07</t>
+          <t>29434.7894310522</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>27.82</t>
+          <t>26365.5260503027</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>26.86</t>
+          <t>24099.328130321</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>26.67</t>
+          <t>23518.8618626669</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>25.89</t>
+          <t>22374.8318174798</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>25.15</t>
+          <t>20485.1236655733</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>24.41</t>
+          <t>21545.0830131354</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>23.62</t>
+          <t>22378.5344811173</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>22.6</t>
+          <t>26699.28266116</t>
         </is>
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>21.08</t>
+          <t>29702.3915195364</t>
         </is>
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>20.76</t>
+          <t>30476.6065741515</t>
         </is>
       </c>
       <c r="N19" t="inlineStr">
         <is>
-          <t>20.05</t>
+          <t>31487.5915397625</t>
         </is>
       </c>
       <c r="O19" t="inlineStr">
         <is>
-          <t>19.36</t>
+          <t>35722.9024123712</t>
         </is>
       </c>
       <c r="P19" t="inlineStr">
         <is>
-          <t>18.87</t>
+          <t>0</t>
         </is>
       </c>
       <c r="Q19" t="inlineStr">
         <is>
-          <t>17.57</t>
+          <t>0</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Exchange rate (USD)</t>
+          <t>Labour force value (magnitude of value)</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>exchange.r.us</t>
+          <t>labour_force_value.m.mv</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>0.733573431220508</t>
+          <t>1256.32379163273</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>0.772272322275964</t>
+          <t>1276.8196897925</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>0.871915557756043</t>
+          <t>1068.05129416122</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>0.89762575613992</t>
+          <t>1132.00123921374</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>0.938262378300011</t>
+          <t>1138.51819402256</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>1.08271976614765</t>
+          <t>1025.86524230699</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>1.11656987699161</t>
+          <t>1051.70980345528</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>1.05752963905731</t>
+          <t>1062.0390358881</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>0.884017007086561</t>
+          <t>1182.71625500153</t>
         </is>
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>0.803923182182888</t>
+          <t>1241.54655439266</t>
         </is>
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>0.803793922960251</t>
+          <t>1263.42107475627</t>
         </is>
       </c>
       <c r="N20" t="inlineStr">
         <is>
-          <t>0.796431999450991</t>
+          <t>1305.14977817888</t>
         </is>
       </c>
       <c r="O20" t="inlineStr">
         <is>
-          <t>0.729660723656212</t>
+          <t>1299.52811517305</t>
         </is>
       </c>
       <c r="P20" t="inlineStr">
         <is>
-          <t>0.67990207486318</t>
+          <t>1268.50148211206</t>
         </is>
       </c>
       <c r="Q20" t="inlineStr">
         <is>
-          <t>0.716948692920124</t>
+          <t>1178.07144714241</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Compensation of employees (USD)</t>
+          <t>Value transfer through trade</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>compensation.empe.s.us</t>
+          <t>trade_transfers.s.mv</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>0.065</t>
+          <t>3158969273.10728</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>0.064</t>
+          <t>3138440591.84057</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>0.06</t>
+          <t>2774341364.8589</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>0.063</t>
+          <t>3343936924.14956</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>0.063</t>
+          <t>3725067714.35627</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>0.058</t>
+          <t>3460538620.1831</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>0.06</t>
+          <t>3675135616.74461</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>0.065</t>
+          <t>3876023359.52019</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>0.08</t>
+          <t>4138241509.30518</t>
         </is>
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>0.091</t>
+          <t>4395559675.01542</t>
         </is>
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>0.096</t>
+          <t>3965303025.95346</t>
         </is>
       </c>
       <c r="N21" t="inlineStr">
         <is>
-          <t>0.101</t>
+          <t>4219540785.55398</t>
         </is>
       </c>
       <c r="O21" t="inlineStr">
         <is>
-          <t>0.117</t>
+          <t>4522699943.72215</t>
         </is>
       </c>
       <c r="P21" t="inlineStr">
         <is>
-          <t>0.134</t>
+          <t>4424694859.72343</t>
         </is>
       </c>
       <c r="Q21" t="inlineStr">
         <is>
-          <t>0.126</t>
+          <t>3114892277.30925</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Labour compensation (USD)</t>
+          <t>Value transfer through trade of productive sectors</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>compensation.emp.s.us</t>
+          <t>trade_transfers.p.s.mv</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>0.077</t>
+          <t>3787446363.19668</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>0.076</t>
+          <t>3723508219.53801</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>0.071</t>
+          <t>3340314713.41904</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>0.073</t>
+          <t>3856821473.82079</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>0.073</t>
+          <t>4146453346.45742</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>0.067</t>
+          <t>4119592444.73038</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>0.069</t>
+          <t>4138035550.37509</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>0.075</t>
+          <t>4323135023.68019</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>0.092</t>
+          <t>4745813725.57159</t>
         </is>
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>0.105</t>
+          <t>5037461357.08971</t>
         </is>
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>0.111</t>
+          <t>4692899968.77375</t>
         </is>
       </c>
       <c r="N22" t="inlineStr">
         <is>
-          <t>0.117</t>
+          <t>4959463361.45794</t>
         </is>
       </c>
       <c r="O22" t="inlineStr">
         <is>
-          <t>0.135</t>
+          <t>5407464106.54054</t>
         </is>
       </c>
       <c r="P22" t="inlineStr">
         <is>
-          <t>0.155</t>
+          <t>5492279452.38023</t>
         </is>
       </c>
       <c r="Q22" t="inlineStr">
         <is>
-          <t>0.145</t>
+          <t>3981188442.8356</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Capital stock (USD)</t>
+          <t>Value transfer through trade of unproductive sectors</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>capital_stock.s.us</t>
+          <t>trade_transfers.u.s.mv</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>0.435</t>
+          <t>-628477090.089403</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>0.413</t>
+          <t>-585067627.697437</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>0.382</t>
+          <t>-565973348.560143</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>0.389</t>
+          <t>-512884549.671236</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>0.39</t>
+          <t>-421385632.101142</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>0.364</t>
+          <t>-659053824.547273</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>0.383</t>
+          <t>-462899933.630477</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>0.407</t>
+          <t>-447111664.159997</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>0.492</t>
+          <t>-607572216.266412</t>
         </is>
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>0.561</t>
+          <t>-641901682.074284</t>
         </is>
       </c>
       <c r="M23" t="inlineStr">
         <is>
-          <t>0.593</t>
+          <t>-727596942.820282</t>
         </is>
       </c>
       <c r="N23" t="inlineStr">
         <is>
-          <t>0.63</t>
+          <t>-739922575.903958</t>
         </is>
       </c>
       <c r="O23" t="inlineStr">
         <is>
-          <t>0.735</t>
+          <t>-884764162.818395</t>
         </is>
       </c>
       <c r="P23" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>-1067584592.6568</t>
         </is>
       </c>
       <c r="Q23" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>-866296165.526347</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Gross output (USD)</t>
+          <t>Working day of employee per year (magnitude of value)</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>gross_output.s.us</t>
+          <t>abstract_labour.empe.m.mv</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>0.24</t>
+          <t>1653.2144268217</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>0.238</t>
+          <t>1646.8986216096</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>0.229</t>
+          <t>1650.63793288303</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>0.24</t>
+          <t>1645.97437766899</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>0.241</t>
+          <t>1643.37973783152</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>0.235</t>
+          <t>1636.61650027318</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>0.234</t>
+          <t>1627.96820907894</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>0.252</t>
+          <t>1624.17529496749</t>
         </is>
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>0.307</t>
+          <t>1622.18162588337</t>
         </is>
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>0.357</t>
+          <t>1626.76562125928</t>
         </is>
       </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t>0.377</t>
+          <t>1621.81423447234</t>
         </is>
       </c>
       <c r="N24" t="inlineStr">
         <is>
-          <t>0.413</t>
+          <t>1618.81762875586</t>
         </is>
       </c>
       <c r="O24" t="inlineStr">
         <is>
-          <t>0.488</t>
+          <t>1618.69719269556</t>
         </is>
       </c>
       <c r="P24" t="inlineStr">
         <is>
-          <t>0.552</t>
+          <t>1620.65261178998</t>
         </is>
       </c>
       <c r="Q24" t="inlineStr">
         <is>
-          <t>0.47</t>
+          <t>1592.33158699986</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Gross Domestic Product (USD)</t>
+          <t>Working day of persons engaged per year (magnitude of value)</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>gdp.s.us</t>
+          <t>abstract_labour.emp.m.mv</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>0.114</t>
+          <t>1776.09977103327</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>0.112</t>
+          <t>1775.0024017677</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>0.106</t>
+          <t>1770.54205954759</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>0.112</t>
+          <t>1760.66037305605</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>0.113</t>
+          <t>1764.28444286223</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>0.106</t>
+          <t>1750.63224906253</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>0.109</t>
+          <t>1732.98339213493</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>0.119</t>
+          <t>1726.11030602677</t>
         </is>
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>0.143</t>
+          <t>1718.73402623956</t>
         </is>
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>0.165</t>
+          <t>1723.23815180958</t>
         </is>
       </c>
       <c r="M25" t="inlineStr">
         <is>
-          <t>0.17</t>
+          <t>1715.80445337351</t>
         </is>
       </c>
       <c r="N25" t="inlineStr">
         <is>
-          <t>0.18</t>
+          <t>1708.77856320894</t>
         </is>
       </c>
       <c r="O25" t="inlineStr">
         <is>
-          <t>0.215</t>
+          <t>1706.36740275934</t>
         </is>
       </c>
       <c r="P25" t="inlineStr">
         <is>
-          <t>0.238</t>
+          <t>1689.51690175521</t>
         </is>
       </c>
       <c r="Q25" t="inlineStr">
         <is>
-          <t>0.208</t>
+          <t>1669.02688174569</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Rate of surplus value of high-skilled employee</t>
+          <t>Total exports (USD)</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>surplus_value.empe_hs.r.pc</t>
+          <t>exports.s.us</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>10.82</t>
+          <t>46602.1927758937</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>8.6</t>
+          <t>46729.9583041946</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>30.71</t>
+          <t>46493.8429920393</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>21.05</t>
+          <t>48793.8311815811</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>17.79</t>
+          <t>49564.3941345042</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>29.22</t>
+          <t>51553.402734727</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>27.09</t>
+          <t>50362.3725617934</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>25.31</t>
+          <t>53089.8310980472</t>
         </is>
       </c>
       <c r="K26" t="inlineStr">
         <is>
-          <t>17.01</t>
+          <t>61683.8070180424</t>
         </is>
       </c>
       <c r="L26" t="inlineStr">
         <is>
-          <t>6.46</t>
+          <t>73102.2887236213</t>
         </is>
       </c>
       <c r="M26" t="inlineStr">
         <is>
-          <t>3.66</t>
+          <t>79071.6106660618</t>
         </is>
       </c>
       <c r="N26" t="inlineStr">
         <is>
-          <t>-0.15</t>
+          <t>91424.9950671943</t>
         </is>
       </c>
       <c r="O26" t="inlineStr">
         <is>
-          <t>-0.83</t>
+          <t>109319.492699324</t>
         </is>
       </c>
       <c r="P26" t="inlineStr">
         <is>
-          <t>1.54</t>
+          <t>123398.018391332</t>
         </is>
       </c>
       <c r="Q26" t="inlineStr">
         <is>
-          <t>7.85</t>
+          <t>87225.8247802957</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Rate of surplus value of medium-skilled employee</t>
+          <t>Total exports (magnitude of value)</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>surplus_value.empe_ms.r.pc</t>
+          <t>exports.s.mv</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>46.19</t>
+          <t>1625077790.09856</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>43.33</t>
+          <t>1629150580.92762</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>71.25</t>
+          <t>1636894505.09432</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>60.41</t>
+          <t>1752829522.48198</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>61.06</t>
+          <t>1912985002.5353</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>78.31</t>
+          <t>2094350806.54158</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>72.03</t>
+          <t>1954326150.58722</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>70.6</t>
+          <t>1928353841.32507</t>
         </is>
       </c>
       <c r="K27" t="inlineStr">
         <is>
-          <t>52.29</t>
+          <t>1958663055.05986</t>
         </is>
       </c>
       <c r="L27" t="inlineStr">
         <is>
-          <t>48.44</t>
+          <t>2075565816.3358</t>
         </is>
       </c>
       <c r="M27" t="inlineStr">
         <is>
-          <t>46.46</t>
+          <t>2140084745.31965</t>
         </is>
       </c>
       <c r="N27" t="inlineStr">
         <is>
-          <t>42.48</t>
+          <t>2326896079.94659</t>
         </is>
       </c>
       <c r="O27" t="inlineStr">
         <is>
-          <t>46.74</t>
+          <t>2402567824.3385</t>
         </is>
       </c>
       <c r="P27" t="inlineStr">
         <is>
-          <t>52.29</t>
+          <t>2215180740.01896</t>
         </is>
       </c>
       <c r="Q27" t="inlineStr">
         <is>
-          <t>62.59</t>
+          <t>1415626035.71592</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Rate of surplus value of low-skilled employee</t>
+          <t>Total imports (USD)</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>surplus_value.empe_ls.r.pc</t>
+          <t>imports.s.us</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>42.98</t>
+          <t>35247.6713112743</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>40.91</t>
+          <t>36045.8139090302</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>68.74</t>
+          <t>35691.4596345649</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>63.99</t>
+          <t>36485.122976794</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>66.39</t>
+          <t>36014.1148455671</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>86.28</t>
+          <t>38668.4687917521</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>79.82</t>
+          <t>37248.947742656</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>79.07</t>
+          <t>39039.1196999104</t>
         </is>
       </c>
       <c r="K28" t="inlineStr">
         <is>
-          <t>49.5</t>
+          <t>48458.4510333796</t>
         </is>
       </c>
       <c r="L28" t="inlineStr">
         <is>
-          <t>55.65</t>
+          <t>58277.7921699471</t>
         </is>
       </c>
       <c r="M28" t="inlineStr">
         <is>
-          <t>52.84</t>
+          <t>68175.8269779987</t>
         </is>
       </c>
       <c r="N28" t="inlineStr">
         <is>
-          <t>47.91</t>
+          <t>78162.4060985394</t>
         </is>
       </c>
       <c r="O28" t="inlineStr">
         <is>
-          <t>46.86</t>
+          <t>92552.1690788116</t>
         </is>
       </c>
       <c r="P28" t="inlineStr">
         <is>
-          <t>47.72</t>
+          <t>108837.962921108</t>
         </is>
       </c>
       <c r="Q28" t="inlineStr">
         <is>
-          <t>57.17</t>
+          <t>79860.246117199</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Hours of abstract labour</t>
+          <t>Total imports (magnitude of value)</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>abstract_labour.emp.s.mv</t>
+          <t>imports.s.mv</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>3645.8</t>
+          <t>3030707875.28384</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>3695.2</t>
+          <t>3183915774.60494</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>3811.8</t>
+          <t>2932921839.78823</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>3860.6</t>
+          <t>3323641172.77424</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>3964.7</t>
+          <t>3642043203.92278</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>4014.9</t>
+          <t>3642075940.24484</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>4027.8</t>
+          <t>3582405653.56493</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>4049.8</t>
+          <t>3635437249.28312</t>
         </is>
       </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t>4034.9</t>
+          <t>4170871347.96143</t>
         </is>
       </c>
       <c r="L29" t="inlineStr">
         <is>
-          <t>4061.5</t>
+          <t>4491386799.74022</t>
         </is>
       </c>
       <c r="M29" t="inlineStr">
         <is>
-          <t>4099.4</t>
+          <t>4756640843.3598</t>
         </is>
       </c>
       <c r="N29" t="inlineStr">
         <is>
-          <t>4157.8</t>
+          <t>5049047096.30021</t>
         </is>
       </c>
       <c r="O29" t="inlineStr">
         <is>
-          <t>4242.2</t>
+          <t>5256050002.69841</t>
         </is>
       </c>
       <c r="P29" t="inlineStr">
         <is>
-          <t>4292.752</t>
+          <t>5356928219.64953</t>
         </is>
       </c>
       <c r="Q29" t="inlineStr">
         <is>
-          <t>4119.799</t>
+          <t>3816914982.21976</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Hours of abstract labour (employee only)</t>
+          <t>Trade balance (USD)</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>abstract_labour.empe.s.mv</t>
+          <t>trade_balance.s.us</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>2929</t>
+          <t>11354.5214646194</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>2963.1</t>
+          <t>10684.1443951645</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>3079.1</t>
+          <t>10802.3833574745</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>3160.6</t>
+          <t>12308.7082047871</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>3234.5</t>
+          <t>13550.2792889371</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>3295</t>
+          <t>12884.9339429749</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>3338.8</t>
+          <t>13113.4248191374</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>3372.6</t>
+          <t>14050.7113981367</t>
         </is>
       </c>
       <c r="K30" t="inlineStr">
         <is>
-          <t>3374.3</t>
+          <t>13225.3559846628</t>
         </is>
       </c>
       <c r="L30" t="inlineStr">
         <is>
-          <t>3397.5</t>
+          <t>14824.4965536741</t>
         </is>
       </c>
       <c r="M30" t="inlineStr">
         <is>
-          <t>3436.3</t>
+          <t>10895.7836880631</t>
         </is>
       </c>
       <c r="N30" t="inlineStr">
         <is>
-          <t>3485.8</t>
+          <t>13262.5889686549</t>
         </is>
       </c>
       <c r="O30" t="inlineStr">
         <is>
-          <t>3563.4</t>
+          <t>16767.3236205123</t>
         </is>
       </c>
       <c r="P30" t="inlineStr">
         <is>
-          <t>3620.7</t>
+          <t>14560.0554702245</t>
         </is>
       </c>
       <c r="Q30" t="inlineStr">
         <is>
-          <t>3434.5</t>
+          <t>7365.57866309673</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Gross output (magnitude of value)</t>
+          <t>Trade balance (magnitude of value)</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>gross_output.s.mv</t>
+          <t>trade_balance.s.mv</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>6717.255</t>
+          <t>-1405630085.18528</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>6597.238</t>
+          <t>-1554765193.67732</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>6429.136</t>
+          <t>-1296027334.69391</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>6839.987</t>
+          <t>-1570811650.29226</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>7240.457</t>
+          <t>-1729058201.38748</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>7279.794</t>
+          <t>-1547725133.70326</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>6964.996</t>
+          <t>-1628079502.97771</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>6879.373</t>
+          <t>-1707083407.95804</t>
         </is>
       </c>
       <c r="K31" t="inlineStr">
         <is>
-          <t>7229.551</t>
+          <t>-2212208292.90157</t>
         </is>
       </c>
       <c r="L31" t="inlineStr">
         <is>
-          <t>7429.944</t>
+          <t>-2415820983.40443</t>
         </is>
       </c>
       <c r="M31" t="inlineStr">
         <is>
-          <t>7667.354</t>
+          <t>-2616556098.04014</t>
         </is>
       </c>
       <c r="N31" t="inlineStr">
         <is>
-          <t>8025.579</t>
+          <t>-2722151016.35361</t>
         </is>
       </c>
       <c r="O31" t="inlineStr">
         <is>
-          <t>8171.624</t>
+          <t>-2853482178.35991</t>
         </is>
       </c>
       <c r="P31" t="inlineStr">
         <is>
-          <t>7656.679</t>
+          <t>-3141747479.63058</t>
         </is>
       </c>
       <c r="Q31" t="inlineStr">
         <is>
-          <t>5668.044</t>
+          <t>-2401288946.50384</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Gross output (direct prices - USD)</t>
+          <t>Gross Domestic Product of productive sectors (USD)</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>gross_output.s.du</t>
+          <t>gdp.p.s.us</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>0.052</t>
+          <t>64200.79909</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>0.052</t>
+          <t>61759.30231</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>0.05</t>
+          <t>58503.37221</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>0.053</t>
+          <t>62327.75749</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>0.058</t>
+          <t>61869.68785</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>0.06</t>
+          <t>58261.61286</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>0.056</t>
+          <t>59201.8479</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>0.056</t>
+          <t>63413.82581</t>
         </is>
       </c>
       <c r="K32" t="inlineStr">
         <is>
-          <t>0.064</t>
+          <t>76507.57744</t>
         </is>
       </c>
       <c r="L32" t="inlineStr">
         <is>
-          <t>0.072</t>
+          <t>87157.58111</t>
         </is>
       </c>
       <c r="M32" t="inlineStr">
         <is>
-          <t>0.08</t>
+          <t>90008.14496</t>
         </is>
       </c>
       <c r="N32" t="inlineStr">
         <is>
-          <t>0.088</t>
+          <t>96229.18212</t>
         </is>
       </c>
       <c r="O32" t="inlineStr">
         <is>
-          <t>0.101</t>
+          <t>115291.93935</t>
         </is>
       </c>
       <c r="P32" t="inlineStr">
         <is>
-          <t>0.105</t>
+          <t>124463.51194</t>
         </is>
       </c>
       <c r="Q32" t="inlineStr">
         <is>
-          <t>0.072</t>
+          <t>103229.14414</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Gross Domestic Product (magnitude of value)</t>
+          <t>Rate of profit</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>gdp.s.mv</t>
+          <t>appropriated_profit.r.pc</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>2206.7</t>
+          <t>0.0189138531738914</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>2212.3</t>
+          <t>0.0225221645238238</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>2275.8</t>
+          <t>0.0299252922407378</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>2297.2</t>
+          <t>0.0403953505507245</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>2345.1</t>
+          <t>0.0432499521060523</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>2354.1</t>
+          <t>0.0505733244248037</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>2341.4</t>
+          <t>0.0485089947592811</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>2334.9</t>
+          <t>0.0521776595090084</t>
         </is>
       </c>
       <c r="K33" t="inlineStr">
         <is>
-          <t>2305.4</t>
+          <t>0.0489114758100198</t>
         </is>
       </c>
       <c r="L33" t="inlineStr">
         <is>
-          <t>2308.6</t>
+          <t>0.0533423397070572</t>
         </is>
       </c>
       <c r="M33" t="inlineStr">
         <is>
-          <t>2318.4</t>
+          <t>0.0487240812627278</t>
         </is>
       </c>
       <c r="N33" t="inlineStr">
         <is>
-          <t>2352.5</t>
+          <t>0.0508234311114752</t>
         </is>
       </c>
       <c r="O33" t="inlineStr">
         <is>
-          <t>2388.6</t>
+          <t>0.0604489780828278</t>
         </is>
       </c>
       <c r="P33" t="inlineStr">
         <is>
-          <t>2415.662</t>
+          <t>0</t>
         </is>
       </c>
       <c r="Q33" t="inlineStr">
         <is>
-          <t>2282.511</t>
+          <t>0</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Gross Domestic Product (direct prices - USD)</t>
+          <t>Compensation of employees (USD)</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>gdp.s.du</t>
+          <t>compensation.empe.s.us</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>0.017</t>
+          <t>64780.1545720892</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>0.017</t>
+          <t>64117.2790306618</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>0.018</t>
+          <t>59836.0697050603</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>0.018</t>
+          <t>62504.8914512194</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>0.019</t>
+          <t>62601.8923411265</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>0.019</t>
+          <t>57618.7875727284</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>0.019</t>
+          <t>59520.6814993623</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>0.019</t>
+          <t>64725.3726908649</t>
         </is>
       </c>
       <c r="K34" t="inlineStr">
         <is>
-          <t>0.02</t>
+          <t>79674.9373851652</t>
         </is>
       </c>
       <c r="L34" t="inlineStr">
         <is>
-          <t>0.022</t>
+          <t>91179.109613634</t>
         </is>
       </c>
       <c r="M34" t="inlineStr">
         <is>
-          <t>0.024</t>
+          <t>95969.8720259783</t>
         </is>
       </c>
       <c r="N34" t="inlineStr">
         <is>
-          <t>0.026</t>
+          <t>101251.582030597</t>
         </is>
       </c>
       <c r="O34" t="inlineStr">
         <is>
-          <t>0.03</t>
+          <t>117111.963314036</t>
         </is>
       </c>
       <c r="P34" t="inlineStr">
         <is>
-          <t>0.033</t>
+          <t>133967.8212127</t>
         </is>
       </c>
       <c r="Q34" t="inlineStr">
         <is>
-          <t>0.029</t>
+          <t>126339.07733036</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Total labour force value (magnitude of value)</t>
+          <t>Labour compensation (USD)</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>labour_force_value.s.mv</t>
+          <t>compensation.emp.s.us</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>2225.829</t>
+          <t>76548.6526088396</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>2297.254</t>
+          <t>75928.4406545897</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>1992.343</t>
+          <t>70740.1372455899</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>2173.669</t>
+          <t>73138.9017173403</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>2240.832</t>
+          <t>73475.8848258086</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>2065.374</t>
+          <t>67381.129906586</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>2156.952</t>
+          <t>69040.5710335755</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>2205.324</t>
+          <t>74896.1260440397</t>
         </is>
       </c>
       <c r="K35" t="inlineStr">
         <is>
-          <t>2460.168</t>
+          <t>91922.7636145912</t>
         </is>
       </c>
       <c r="L35" t="inlineStr">
         <is>
-          <t>2592.97</t>
+          <t>105216.960221896</t>
         </is>
       </c>
       <c r="M35" t="inlineStr">
         <is>
-          <t>2676.937</t>
+          <t>110653.750386334</t>
         </is>
       </c>
       <c r="N35" t="inlineStr">
         <is>
-          <t>2810.379</t>
+          <t>116859.797080634</t>
         </is>
       </c>
       <c r="O35" t="inlineStr">
         <is>
-          <t>2860.781</t>
+          <t>134984.0403848</t>
         </is>
       </c>
       <c r="P35" t="inlineStr">
         <is>
-          <t>2833.959</t>
+          <t>154720.822196622</t>
         </is>
       </c>
       <c r="Q35" t="inlineStr">
         <is>
-          <t>2540.982</t>
+          <t>145394.444269938</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Rate of surplus value</t>
+          <t>Capital stock (USD)</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>surplus_value.empe.r.pc</t>
+          <t>capital_stock.s.us</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>31.59</t>
+          <t>434990.525963539</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>28.98</t>
+          <t>412643.00441802</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>54.55</t>
+          <t>381606.223665989</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>45.4</t>
+          <t>388762.780515372</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>44.34</t>
+          <t>389772.201027538</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>59.54</t>
+          <t>364000.321458247</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>54.79</t>
+          <t>383057.173530358</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>52.93</t>
+          <t>407346.842208847</t>
         </is>
       </c>
       <c r="K36" t="inlineStr">
         <is>
-          <t>37.16</t>
+          <t>492317.157588525</t>
         </is>
       </c>
       <c r="L36" t="inlineStr">
         <is>
-          <t>31.03</t>
+          <t>560784.573433505</t>
         </is>
       </c>
       <c r="M36" t="inlineStr">
         <is>
-          <t>28.37</t>
+          <t>592896.670205935</t>
         </is>
       </c>
       <c r="N36" t="inlineStr">
         <is>
-          <t>24.03</t>
+          <t>630188.406590516</t>
         </is>
       </c>
       <c r="O36" t="inlineStr">
         <is>
-          <t>24.56</t>
+          <t>734524.414821197</t>
         </is>
       </c>
       <c r="P36" t="inlineStr">
         <is>
-          <t>27.76</t>
+          <t>0</t>
         </is>
       </c>
       <c r="Q36" t="inlineStr">
         <is>
-          <t>35.16</t>
+          <t>0</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Value per output</t>
+          <t>Total real wage (constant USD)</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>value.m.mv</t>
+          <t>compensation.emp.s.cu</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>0.988</t>
+          <t>76548.6526088396</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>0.985</t>
+          <t>80020.2330856799</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>0.999</t>
+          <t>83389.1472750524</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>1.032</t>
+          <t>85332.2044840451</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>1.132</t>
+          <t>88639.7472275423</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>1.174</t>
+          <t>91440.1570608733</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>1.117</t>
+          <t>93124.6963278419</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>1.045</t>
+          <t>94367.3206985582</t>
         </is>
       </c>
       <c r="K37" t="inlineStr">
         <is>
-          <t>0.932</t>
+          <t>96812.5996990925</t>
         </is>
       </c>
       <c r="L37" t="inlineStr">
         <is>
-          <t>0.816</t>
+          <t>99869.768988331</t>
         </is>
       </c>
       <c r="M37" t="inlineStr">
         <is>
-          <t>0.796</t>
+          <t>104735.859668845</t>
         </is>
       </c>
       <c r="N37" t="inlineStr">
         <is>
-          <t>0.754</t>
+          <t>109401.97646161</t>
         </is>
       </c>
       <c r="O37" t="inlineStr">
         <is>
-          <t>0.636</t>
+          <t>111988.208159261</t>
         </is>
       </c>
       <c r="P37" t="inlineStr">
         <is>
-          <t>0.533</t>
+          <t>117681.767594062</t>
         </is>
       </c>
       <c r="Q37" t="inlineStr">
         <is>
-          <t>0.491</t>
+          <t>117869.305008202</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>Total real compensation of labour (constant USD)</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>compensation.empe.s.cu</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>64780.1545720892</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>67653.4194594542</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>70695.8077077831</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>73108.0423646639</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>76078.7651134119</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>78744.0237285374</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>80912.5039189161</t>
+        </is>
+      </c>
+      <c r="J38" t="inlineStr">
+        <is>
+          <t>82068.4674150358</t>
+        </is>
+      </c>
+      <c r="K38" t="inlineStr">
+        <is>
+          <t>84607.7513643575</t>
+        </is>
+      </c>
+      <c r="L38" t="inlineStr">
+        <is>
+          <t>87367.4140641673</t>
+        </is>
+      </c>
+      <c r="M38" t="inlineStr">
+        <is>
+          <t>91812.1413447876</t>
+        </is>
+      </c>
+      <c r="N38" t="inlineStr">
+        <is>
+          <t>95751.0737689078</t>
+        </is>
+      </c>
+      <c r="O38" t="inlineStr">
+        <is>
+          <t>98755.6331667538</t>
+        </is>
+      </c>
+      <c r="P38" t="inlineStr">
+        <is>
+          <t>103743.762731314</t>
+        </is>
+      </c>
+      <c r="Q38" t="inlineStr">
+        <is>
+          <t>103924.800250466</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>Total profit (USD)</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>profit.s.us</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>37662.1363711604</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>35659.1396854103</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>35519.0058944101</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>39223.0706626597</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>39232.4608441914</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>38893.830013414</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>40126.8014364245</t>
+        </is>
+      </c>
+      <c r="J39" t="inlineStr">
+        <is>
+          <t>43632.9393159603</t>
+        </is>
+      </c>
+      <c r="K39" t="inlineStr">
+        <is>
+          <t>50779.2414054088</t>
+        </is>
+      </c>
+      <c r="L39" t="inlineStr">
+        <is>
+          <t>59615.9527381036</t>
+        </is>
+      </c>
+      <c r="M39" t="inlineStr">
+        <is>
+          <t>59364.9521136662</t>
+        </is>
+      </c>
+      <c r="N39" t="inlineStr">
+        <is>
+          <t>63515.9286093659</t>
+        </is>
+      </c>
+      <c r="O39" t="inlineStr">
+        <is>
+          <t>80124.1526651996</t>
+        </is>
+      </c>
+      <c r="P39" t="inlineStr">
+        <is>
+          <t>82819.2677833777</t>
+        </is>
+      </c>
+      <c r="Q39" t="inlineStr">
+        <is>
+          <t>62215.9487400622</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>Hours of abstract labour (employee only)</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>abstract_labour.empe.s.mv</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>2.929e+09</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>2963100000</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>3079100000</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>3160600000</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>3234500000</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>3.295e+09</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>3338800000</t>
+        </is>
+      </c>
+      <c r="J40" t="inlineStr">
+        <is>
+          <t>3372600000</t>
+        </is>
+      </c>
+      <c r="K40" t="inlineStr">
+        <is>
+          <t>3374300000</t>
+        </is>
+      </c>
+      <c r="L40" t="inlineStr">
+        <is>
+          <t>3397500000</t>
+        </is>
+      </c>
+      <c r="M40" t="inlineStr">
+        <is>
+          <t>3436300000</t>
+        </is>
+      </c>
+      <c r="N40" t="inlineStr">
+        <is>
+          <t>3485800000</t>
+        </is>
+      </c>
+      <c r="O40" t="inlineStr">
+        <is>
+          <t>3563400000</t>
+        </is>
+      </c>
+      <c r="P40" t="inlineStr">
+        <is>
+          <t>3620700000</t>
+        </is>
+      </c>
+      <c r="Q40" t="inlineStr">
+        <is>
+          <t>3434500000</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>Hours of abstract labour</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>abstract_labour.emp.s.mv</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>3645800000</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>3695200000</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>3811800000</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>3860600000</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>3964700000</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>4014900000</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>4027800000</t>
+        </is>
+      </c>
+      <c r="J41" t="inlineStr">
+        <is>
+          <t>4049800000</t>
+        </is>
+      </c>
+      <c r="K41" t="inlineStr">
+        <is>
+          <t>4034900000</t>
+        </is>
+      </c>
+      <c r="L41" t="inlineStr">
+        <is>
+          <t>4061500000</t>
+        </is>
+      </c>
+      <c r="M41" t="inlineStr">
+        <is>
+          <t>4099400000</t>
+        </is>
+      </c>
+      <c r="N41" t="inlineStr">
+        <is>
+          <t>4157800000</t>
+        </is>
+      </c>
+      <c r="O41" t="inlineStr">
+        <is>
+          <t>4242200000</t>
+        </is>
+      </c>
+      <c r="P41" t="inlineStr">
+        <is>
+          <t>4292752281.33335</t>
+        </is>
+      </c>
+      <c r="Q41" t="inlineStr">
+        <is>
+          <t>4119798894.31217</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>Gross Domestic Product (magnitude of value)</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>gdp.s.mv</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>2206700000</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>2212300000</t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>2275800000</t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>2297200000</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>2345100000</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>2354100000</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>2341400000</t>
+        </is>
+      </c>
+      <c r="J42" t="inlineStr">
+        <is>
+          <t>2334900000</t>
+        </is>
+      </c>
+      <c r="K42" t="inlineStr">
+        <is>
+          <t>2305400000</t>
+        </is>
+      </c>
+      <c r="L42" t="inlineStr">
+        <is>
+          <t>2308600000</t>
+        </is>
+      </c>
+      <c r="M42" t="inlineStr">
+        <is>
+          <t>2318400000</t>
+        </is>
+      </c>
+      <c r="N42" t="inlineStr">
+        <is>
+          <t>2352500000</t>
+        </is>
+      </c>
+      <c r="O42" t="inlineStr">
+        <is>
+          <t>2388600000</t>
+        </is>
+      </c>
+      <c r="P42" t="inlineStr">
+        <is>
+          <t>2415662342.89855</t>
+        </is>
+      </c>
+      <c r="Q42" t="inlineStr">
+        <is>
+          <t>2282510706.58301</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>Number of persons engaged</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>emp.s.un</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>2052700</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>2081800</t>
+        </is>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>2152900</t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>2192700</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>2247200</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>2293400</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>2324200</t>
+        </is>
+      </c>
+      <c r="J43" t="inlineStr">
+        <is>
+          <t>2346200</t>
+        </is>
+      </c>
+      <c r="K43" t="inlineStr">
+        <is>
+          <t>2347600</t>
+        </is>
+      </c>
+      <c r="L43" t="inlineStr">
+        <is>
+          <t>2356900</t>
+        </is>
+      </c>
+      <c r="M43" t="inlineStr">
+        <is>
+          <t>2389200</t>
+        </is>
+      </c>
+      <c r="N43" t="inlineStr">
+        <is>
+          <t>2433200</t>
+        </is>
+      </c>
+      <c r="O43" t="inlineStr">
+        <is>
+          <t>2486100</t>
+        </is>
+      </c>
+      <c r="P43" t="inlineStr">
+        <is>
+          <t>2540816.41732835</t>
+        </is>
+      </c>
+      <c r="Q43" t="inlineStr">
+        <is>
+          <t>2468383.78660693</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>Number of employee</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>empe.s.un</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>1771700</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>1799200</t>
+        </is>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>1865400</t>
+        </is>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>1920200</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>1968200</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>2013300</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>2050900</t>
+        </is>
+      </c>
+      <c r="J44" t="inlineStr">
+        <is>
+          <t>2076500</t>
+        </is>
+      </c>
+      <c r="K44" t="inlineStr">
+        <is>
+          <t>2080100</t>
+        </is>
+      </c>
+      <c r="L44" t="inlineStr">
+        <is>
+          <t>2088500</t>
+        </is>
+      </c>
+      <c r="M44" t="inlineStr">
+        <is>
+          <t>2118800</t>
+        </is>
+      </c>
+      <c r="N44" t="inlineStr">
+        <is>
+          <t>2153300</t>
+        </is>
+      </c>
+      <c r="O44" t="inlineStr">
+        <is>
+          <t>2201400</t>
+        </is>
+      </c>
+      <c r="P44" t="inlineStr">
+        <is>
+          <t>2234100</t>
+        </is>
+      </c>
+      <c r="Q44" t="inlineStr">
+        <is>
+          <t>2156900</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>Total hours worked by persons engaged</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>hours_worked.emp.s.hr</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>3645800000</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>3695200000</t>
+        </is>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>3811800000</t>
+        </is>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>3860600000</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>3964700000</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>4014900000</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>4027800000</t>
+        </is>
+      </c>
+      <c r="J45" t="inlineStr">
+        <is>
+          <t>4049800000</t>
+        </is>
+      </c>
+      <c r="K45" t="inlineStr">
+        <is>
+          <t>4034900000</t>
+        </is>
+      </c>
+      <c r="L45" t="inlineStr">
+        <is>
+          <t>4061500000</t>
+        </is>
+      </c>
+      <c r="M45" t="inlineStr">
+        <is>
+          <t>4099400000</t>
+        </is>
+      </c>
+      <c r="N45" t="inlineStr">
+        <is>
+          <t>4157800000</t>
+        </is>
+      </c>
+      <c r="O45" t="inlineStr">
+        <is>
+          <t>4242200000</t>
+        </is>
+      </c>
+      <c r="P45" t="inlineStr">
+        <is>
+          <t>4292752281.33335</t>
+        </is>
+      </c>
+      <c r="Q45" t="inlineStr">
+        <is>
+          <t>4119798894.31217</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>Total hours worked by employees</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>hours_worked.empe.s.hr</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>2.929e+09</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>2963100000</t>
+        </is>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>3079100000</t>
+        </is>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>3160600000</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>3234500000</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>3.295e+09</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>3338800000</t>
+        </is>
+      </c>
+      <c r="J46" t="inlineStr">
+        <is>
+          <t>3372600000</t>
+        </is>
+      </c>
+      <c r="K46" t="inlineStr">
+        <is>
+          <t>3374300000</t>
+        </is>
+      </c>
+      <c r="L46" t="inlineStr">
+        <is>
+          <t>3397500000</t>
+        </is>
+      </c>
+      <c r="M46" t="inlineStr">
+        <is>
+          <t>3436300000</t>
+        </is>
+      </c>
+      <c r="N46" t="inlineStr">
+        <is>
+          <t>3485800000</t>
+        </is>
+      </c>
+      <c r="O46" t="inlineStr">
+        <is>
+          <t>3563400000</t>
+        </is>
+      </c>
+      <c r="P46" t="inlineStr">
+        <is>
+          <t>3620700000</t>
+        </is>
+      </c>
+      <c r="Q46" t="inlineStr">
+        <is>
+          <t>3434500000</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>Share of high-skilled labour compensation</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>compensation.empe_hs.r.pc</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>0.318785191966435</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>0.325242969869431</t>
+        </is>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>0.328975048732311</t>
+        </is>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>0.33456523972237</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>0.345601204103223</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>0.347387444600473</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr">
+        <is>
+          <t>0.348525926203091</t>
+        </is>
+      </c>
+      <c r="J47" t="inlineStr">
+        <is>
+          <t>0.353739437247561</t>
+        </is>
+      </c>
+      <c r="K47" t="inlineStr">
+        <is>
+          <t>0.341164951748857</t>
+        </is>
+      </c>
+      <c r="L47" t="inlineStr">
+        <is>
+          <t>0.37058464701845</t>
+        </is>
+      </c>
+      <c r="M47" t="inlineStr">
+        <is>
+          <t>0.374091954269727</t>
+        </is>
+      </c>
+      <c r="N47" t="inlineStr">
+        <is>
+          <t>0.379122833708382</t>
+        </is>
+      </c>
+      <c r="O47" t="inlineStr">
+        <is>
+          <t>0.396175341819239</t>
+        </is>
+      </c>
+      <c r="P47" t="inlineStr">
+        <is>
+          <t>0.403158238395283</t>
+        </is>
+      </c>
+      <c r="Q47" t="inlineStr">
+        <is>
+          <t>0.420199510053656</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>Share of medium-skilled labour compensation</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>compensation.empe_ms.r.pc</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>0.402729758764687</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>0.408709118495148</t>
+        </is>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>0.414861778032466</t>
+        </is>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>0.418897551821378</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>0.419807628286951</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>0.426340817820327</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr">
+        <is>
+          <t>0.432089115527316</t>
+        </is>
+      </c>
+      <c r="J48" t="inlineStr">
+        <is>
+          <t>0.435300420804858</t>
+        </is>
+      </c>
+      <c r="K48" t="inlineStr">
+        <is>
+          <t>0.439944509231172</t>
+        </is>
+      </c>
+      <c r="L48" t="inlineStr">
+        <is>
+          <t>0.442742323919603</t>
+        </is>
+      </c>
+      <c r="M48" t="inlineStr">
+        <is>
+          <t>0.442416584481061</t>
+        </is>
+      </c>
+      <c r="N48" t="inlineStr">
+        <is>
+          <t>0.444235964690608</t>
+        </is>
+      </c>
+      <c r="O48" t="inlineStr">
+        <is>
+          <t>0.430430710493054</t>
+        </is>
+      </c>
+      <c r="P48" t="inlineStr">
+        <is>
+          <t>0.42698941120088</t>
+        </is>
+      </c>
+      <c r="Q48" t="inlineStr">
+        <is>
+          <t>0.422997689638566</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>Share of low-skilled labour compensation</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>compensation.empe_ls.r.pc</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>0.278485049268878</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>0.26604791163542</t>
+        </is>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>0.256163173235223</t>
+        </is>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>0.246537208456252</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>0.234591167609826</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>0.2262717375792</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr">
+        <is>
+          <t>0.219384958269592</t>
+        </is>
+      </c>
+      <c r="J49" t="inlineStr">
+        <is>
+          <t>0.210960141947581</t>
+        </is>
+      </c>
+      <c r="K49" t="inlineStr">
+        <is>
+          <t>0.218890539019971</t>
+        </is>
+      </c>
+      <c r="L49" t="inlineStr">
+        <is>
+          <t>0.186673029061948</t>
+        </is>
+      </c>
+      <c r="M49" t="inlineStr">
+        <is>
+          <t>0.183491461249212</t>
+        </is>
+      </c>
+      <c r="N49" t="inlineStr">
+        <is>
+          <t>0.176641201601009</t>
+        </is>
+      </c>
+      <c r="O49" t="inlineStr">
+        <is>
+          <t>0.173393947687707</t>
+        </is>
+      </c>
+      <c r="P49" t="inlineStr">
+        <is>
+          <t>0.169852350403836</t>
+        </is>
+      </c>
+      <c r="Q49" t="inlineStr">
+        <is>
+          <t>0.156802800307778</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>Share of hours worked by high-skilled persons engaged</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>hours_worked.empe_hs.r.pc</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>0.273962792452623</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>0.280187048772489</t>
+        </is>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>0.283290645672041</t>
+        </is>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>0.282732007640922</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>0.285006629270886</t>
+        </is>
+      </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>0.285377458913775</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr">
+        <is>
+          <t>0.288824914960104</t>
+        </is>
+      </c>
+      <c r="J50" t="inlineStr">
+        <is>
+          <t>0.292661282276355</t>
+        </is>
+      </c>
+      <c r="K50" t="inlineStr">
+        <is>
+          <t>0.297260406877777</t>
+        </is>
+      </c>
+      <c r="L50" t="inlineStr">
+        <is>
+          <t>0.303567149908334</t>
+        </is>
+      </c>
+      <c r="M50" t="inlineStr">
+        <is>
+          <t>0.304474725809539</t>
+        </is>
+      </c>
+      <c r="N50" t="inlineStr">
+        <is>
+          <t>0.307989294577137</t>
+        </is>
+      </c>
+      <c r="O50" t="inlineStr">
+        <is>
+          <t>0.316946499155567</t>
+        </is>
+      </c>
+      <c r="P50" t="inlineStr">
+        <is>
+          <t>0.320349632916784</t>
+        </is>
+      </c>
+      <c r="Q50" t="inlineStr">
+        <is>
+          <t>0.337259191383188</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>Share of hours worked by medium-skilled persons engaged</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>hours_worked.empe_ms.r.pc</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>0.435316951886601</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>0.441566304892616</t>
+        </is>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>0.448133256416424</t>
+        </is>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>0.450608738153833</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>0.456051366651535</t>
+        </is>
+      </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>0.463080981079406</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr">
+        <is>
+          <t>0.467042078216123</t>
+        </is>
+      </c>
+      <c r="J51" t="inlineStr">
+        <is>
+          <t>0.471163259919086</t>
+        </is>
+      </c>
+      <c r="K51" t="inlineStr">
+        <is>
+          <t>0.47676111747414</t>
+        </is>
+      </c>
+      <c r="L51" t="inlineStr">
+        <is>
+          <t>0.485667845821841</t>
+        </is>
+      </c>
+      <c r="M51" t="inlineStr">
+        <is>
+          <t>0.487876600547858</t>
+        </is>
+      </c>
+      <c r="N51" t="inlineStr">
+        <is>
+          <t>0.491498400324855</t>
+        </is>
+      </c>
+      <c r="O51" t="inlineStr">
+        <is>
+          <t>0.489432125542819</t>
+        </is>
+      </c>
+      <c r="P51" t="inlineStr">
+        <is>
+          <t>0.490929019346309</t>
+        </is>
+      </c>
+      <c r="Q51" t="inlineStr">
+        <is>
+          <t>0.487053716418833</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>Share of hours worked by low-skilled persons engaged</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>hours_worked.empe_ls.r.pc</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>0.290720255660776</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>0.278246646334896</t>
+        </is>
+      </c>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>0.268576097911535</t>
+        </is>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>0.266659254205245</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>0.258942004077579</t>
+        </is>
+      </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>0.251541560006819</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr">
+        <is>
+          <t>0.244133006823773</t>
+        </is>
+      </c>
+      <c r="J52" t="inlineStr">
+        <is>
+          <t>0.23617545780456</t>
+        </is>
+      </c>
+      <c r="K52" t="inlineStr">
+        <is>
+          <t>0.225978475648083</t>
+        </is>
+      </c>
+      <c r="L52" t="inlineStr">
+        <is>
+          <t>0.210765004269826</t>
+        </is>
+      </c>
+      <c r="M52" t="inlineStr">
+        <is>
+          <t>0.207648673642603</t>
+        </is>
+      </c>
+      <c r="N52" t="inlineStr">
+        <is>
+          <t>0.200512305098008</t>
+        </is>
+      </c>
+      <c r="O52" t="inlineStr">
+        <is>
+          <t>0.193621375301614</t>
+        </is>
+      </c>
+      <c r="P52" t="inlineStr">
+        <is>
+          <t>0.188721347736907</t>
+        </is>
+      </c>
+      <c r="Q52" t="inlineStr">
+        <is>
+          <t>0.175687092197979</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>Gross output (USD)</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>gross_output.s.us</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>239854.6551</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>237907.01329</t>
+        </is>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>229104.75534</t>
+        </is>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>240112.3178</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>241264.06981</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>235411.79038</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr">
+        <is>
+          <t>233919.97869</t>
+        </is>
+      </c>
+      <c r="J53" t="inlineStr">
+        <is>
+          <t>252336.19007</t>
+        </is>
+      </c>
+      <c r="K53" t="inlineStr">
+        <is>
+          <t>306651.34026</t>
+        </is>
+      </c>
+      <c r="L53" t="inlineStr">
+        <is>
+          <t>357016.69779</t>
+        </is>
+      </c>
+      <c r="M53" t="inlineStr">
+        <is>
+          <t>377278.29372</t>
+        </is>
+      </c>
+      <c r="N53" t="inlineStr">
+        <is>
+          <t>413452.74915</t>
+        </is>
+      </c>
+      <c r="O53" t="inlineStr">
+        <is>
+          <t>487841.7983</t>
+        </is>
+      </c>
+      <c r="P53" t="inlineStr">
+        <is>
+          <t>552253.05822</t>
+        </is>
+      </c>
+      <c r="Q53" t="inlineStr">
+        <is>
+          <t>469673.77601</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>Gross Domestic Product (USD)</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>gdp.s.us</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>114210.78898</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>111587.58034</t>
+        </is>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>106259.14314</t>
+        </is>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>112361.97238</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>112708.34567</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>106274.95992</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr">
+        <is>
+          <t>109167.37247</t>
+        </is>
+      </c>
+      <c r="J54" t="inlineStr">
+        <is>
+          <t>118529.06536</t>
+        </is>
+      </c>
+      <c r="K54" t="inlineStr">
+        <is>
+          <t>142702.00502</t>
+        </is>
+      </c>
+      <c r="L54" t="inlineStr">
+        <is>
+          <t>164832.91296</t>
+        </is>
+      </c>
+      <c r="M54" t="inlineStr">
+        <is>
+          <t>170018.7025</t>
+        </is>
+      </c>
+      <c r="N54" t="inlineStr">
+        <is>
+          <t>180375.72569</t>
+        </is>
+      </c>
+      <c r="O54" t="inlineStr">
+        <is>
+          <t>215108.19305</t>
+        </is>
+      </c>
+      <c r="P54" t="inlineStr">
+        <is>
+          <t>237540.08998</t>
+        </is>
+      </c>
+      <c r="Q54" t="inlineStr">
+        <is>
+          <t>207610.39301</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>capital_stock.s.cu</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>319097.493521892</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>324084.115838911</t>
+        </is>
+      </c>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>331309.229914356</t>
+        </is>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>340537.675261471</t>
+        </is>
+      </c>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>349979.093422943</t>
+        </is>
+      </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>359899.739289555</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr">
+        <is>
+          <t>369274.772732724</t>
+        </is>
+      </c>
+      <c r="J55" t="inlineStr">
+        <is>
+          <t>377672.067190042</t>
+        </is>
+      </c>
+      <c r="K55" t="inlineStr">
+        <is>
+          <t>386600.001068428</t>
+        </is>
+      </c>
+      <c r="L55" t="inlineStr">
+        <is>
+          <t>395858.934852572</t>
+        </is>
+      </c>
+      <c r="M55" t="inlineStr">
+        <is>
+          <t>405924.105201978</t>
+        </is>
+      </c>
+      <c r="N55" t="inlineStr">
+        <is>
+          <t>417104.284403962</t>
+        </is>
+      </c>
+      <c r="O55" t="inlineStr">
+        <is>
+          <t>431105.275249461</t>
+        </is>
+      </c>
+      <c r="P55" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Q55" t="inlineStr">
+        <is>
+          <t>0</t>
         </is>
       </c>
     </row>
@@ -3374,7 +4940,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C32"/>
+  <dimension ref="A1:C49"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3397,36 +4963,51 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Capital depreciation (USD)</t>
+          <t>Hours of abstract labour</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>capital_depreciation.s.us</t>
+          <t>abstract_labour.emp.s.mv</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Hours of abstract labour</t>
+          <t>Hours of abstract labour (employee only)</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>abstract_labour.emp.s.mv</t>
+          <t>abstract_labour.empe.s.mv</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Hours of abstract labour (employee only)</t>
+          <t>Number of persons engaged</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>abstract_labour.empe.s.mv</t>
+          <t>emp.s.un</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
@@ -3438,331 +5019,695 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>emp.s.un</t>
+          <t>empe.s.un</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Number of persons engaged</t>
+          <t>Total hours worked by persons engaged</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>empe.s.un</t>
+          <t>hours_worked.emp.s.hr</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Total hours worked by persons engaged</t>
+          <t>Total hours worked by employees</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>hours_worked.emp.s.hr</t>
+          <t>hours_worked.empe.s.hr</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Total hours worked by employees</t>
+          <t>Share of hours worked by high-skilled persons engaged</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>hours_worked.empe.s.hr</t>
+          <t>hours_worked.empe_hs.r.pc</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Share of high-skilled labour compensation</t>
+          <t>Share of hours worked by medium-skilled persons engaged</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>compensation.empe_hs.r.pc</t>
+          <t>hours_worked.empe_ms.r.pc</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Share of medium-skilled labour compensation</t>
+          <t>Share of hours worked by low-skilled persons engaged</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>compensation.empe_ms.r.pc</t>
+          <t>hours_worked.empe_ls.r.pc</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Share of low-skilled labour compensation</t>
+          <t>Share of high-skilled labour compensation</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>compensation.empe_ls.r.pc</t>
+          <t>compensation.empe_hs.r.pc</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Share of hours worked by high-skilled persons engaged</t>
+          <t>Share of medium-skilled labour compensation</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>hours_worked.empe_hs.r.pc</t>
+          <t>compensation.empe_ms.r.pc</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Share of hours worked by medium-skilled persons engaged</t>
+          <t>Share of low-skilled labour compensation</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>hours_worked.empe_ms.r.pc</t>
+          <t>compensation.empe_ls.r.pc</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Share of hours worked by low-skilled persons engaged</t>
+          <t>Compensation of employees (USD)</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>hours_worked.empe_ls.r.pc</t>
+          <t>compensation.empe.s.us</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Exchange rate (USD)</t>
+          <t>Labour compensation (USD)</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>exchange.r.us</t>
+          <t>compensation.emp.s.us</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Compensation of employees (USD)</t>
+          <t>Total labour force value (magnitude of value)</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>compensation.empe.s.us</t>
+          <t>labour_force_value.s.mv</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Labour compensation (USD)</t>
+          <t>Labour force value (magnitude of value)</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>compensation.emp.s.us</t>
+          <t>labour_force_value.m.mv</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Capital stock (USD)</t>
+          <t>Capital depreciation (USD)</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>capital_stock.s.us</t>
+          <t>capital_depreciation.s.us</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Gross output (USD)</t>
+          <t>Capital stock (USD)</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>gross_output.s.us</t>
+          <t>capital_stock.s.us</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Gross output (magnitude of value)</t>
+          <t>Rate of surplus value</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>gross_output.s.mv</t>
+          <t>surplus_value.empe.r.pc</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Gross output (direct prices - USD)</t>
+          <t>Rate of surplus value of high-skilled employee</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>gross_output.s.du</t>
+          <t>surplus_value.empe_hs.r.pc</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Total labour force value (magnitude of value)</t>
+          <t>Rate of surplus value of medium-skilled employee</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>labour_force_value.s.mv</t>
+          <t>surplus_value.empe_ms.r.pc</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Rate of surplus value</t>
+          <t>Rate of surplus value of low-skilled employee</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>surplus_value.empe.r.pc</t>
+          <t>surplus_value.empe_ls.r.pc</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Rate of surplus value of high-skilled employee</t>
+          <t>Gross output (USD)</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>surplus_value.empe_hs.r.pc</t>
+          <t>gross_output.s.us</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Rate of surplus value of medium-skilled employee</t>
+          <t>Gross output (magnitude of value)</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>surplus_value.empe_ms.r.pc</t>
+          <t>gross_output.s.mv</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Rate of surplus value of low-skilled employee</t>
+          <t>Gross output (direct prices - USD)</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>surplus_value.empe_ls.r.pc</t>
+          <t>gross_output.s.du</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Complex labour multiplier</t>
+          <t>Gross Domestic Product (magnitude of value)</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>complex_labour_multiplier.emp.r.un</t>
+          <t>gdp.s.mv</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Complex labour multiplier (employee only)</t>
+          <t>Gross Domestic Product (direct prices - USD)</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>complex_labour_multiplier.empe.r.un</t>
+          <t>gdp.s.du</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Gross Domestic Product (magnitude of value)</t>
+          <t>Gross Domestic Product (USD)</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>gdp.s.mv</t>
+          <t>gdp.s.us</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Gross Domestic Product (direct prices - USD)</t>
+          <t>Value per output</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>gdp.s.du</t>
+          <t>value.m.mv</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Gross Domestic Product (USD)</t>
+          <t>Exchange rate (USD)</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>gdp.s.us</t>
+          <t>exchange.r.us</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Value per output</t>
+          <t>Complex labour multiplier</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>value.m.mv</t>
+          <t>complex_labour_multiplier.emp.r.un</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>NaN</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>Complex labour multiplier (employee only)</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>complex_labour_multiplier.empe.r.un</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>NaN</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>Working day of employee per year (magnitude of value)</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>abstract_labour.empe.m.mv</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>Magnitude of value "created" by employee in each year. Includes productive and unproductive workers.</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>Working day of persons engaged per year (magnitude of value)</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>abstract_labour.emp.m.mv</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>Magnitude of value created by persons engaged in each year. Includes productive and unproductive workers.</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>Total exports (USD)</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>exports.s.us</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>Total exports (magnitude of value)</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>exports.s.mv</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>Total imports (USD)</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>imports.s.us</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>Total imports (magnitude of value)</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>imports.s.mv</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>Trade balance (USD)</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>trade_balance.s.us</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>Trade balance (magnitude of value)</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>trade_balance.s.mv</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>Value transfer through trade</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>trade_transfers.s.mv</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>Value transfer through trade of productive sectors</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>trade_transfers.p.s.mv</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>Value transfer through trade of unproductive sectors</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>trade_transfers.u.s.mv</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>Total real wage (constant USD)</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>compensation.emp.s.cu</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>Total real compensation of labour (constant USD)</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>compensation.empe.s.cu</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>Gross Domestic Product of productive sectors (USD)</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>gdp.p.s.us</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>Total profit (USD)</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>profit.s.us</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>Rate of profit</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>appropriated_profit.r.pc</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
@@ -3799,6 +5744,11 @@
       </c>
     </row>
     <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Reduction Problem: Alternative 1</t>
+        </is>
+      </c>
       <c r="B2" t="inlineStr">
         <is>
           <t>rpA1</t>
